--- a/school_nagatinsky/walls/walls.xlsx
+++ b/school_nagatinsky/walls/walls.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="3" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Общий" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="270">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -1223,6 +1223,18 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1246,18 +1258,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1600,40 +1600,40 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
     </row>
     <row r="5" spans="1:8" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -1668,14 +1668,14 @@
       <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="38"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="42"/>
     </row>
     <row r="7" spans="1:8" ht="18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
@@ -1706,14 +1706,14 @@
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:8" ht="16.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
@@ -1722,14 +1722,14 @@
       <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="38"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
     </row>
     <row r="10" spans="1:8" ht="54" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
@@ -1842,14 +1842,14 @@
       <c r="B15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="38"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
     </row>
     <row r="16" spans="1:8" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -1982,14 +1982,14 @@
       <c r="B22" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="38"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="42"/>
     </row>
     <row r="23" spans="1:8" ht="16.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
@@ -1998,14 +1998,14 @@
       <c r="B23" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="38"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="42"/>
     </row>
     <row r="24" spans="1:8" ht="16.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
@@ -2014,14 +2014,14 @@
       <c r="B24" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="42"/>
     </row>
     <row r="25" spans="1:8" ht="54" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
@@ -2198,14 +2198,14 @@
       <c r="B33" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="38"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="42"/>
     </row>
     <row r="34" spans="1:8" ht="16.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
@@ -2214,14 +2214,14 @@
       <c r="B34" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="38"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="42"/>
     </row>
     <row r="35" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
@@ -2358,14 +2358,14 @@
       <c r="B41" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="36" t="s">
+      <c r="C41" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="38"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="42"/>
     </row>
     <row r="42" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
@@ -2480,14 +2480,14 @@
       <c r="B47" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="36" t="s">
+      <c r="C47" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="38"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="42"/>
     </row>
     <row r="48" spans="1:8" ht="126" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
@@ -2513,7 +2513,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>121</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>79.099999999999994</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>138</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>295.27999999999997</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>150</v>
       </c>
@@ -2832,14 +2832,14 @@
       <c r="B64" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C64" s="36" t="s">
+      <c r="C64" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="38"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="41"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="42"/>
     </row>
     <row r="65" spans="1:8" ht="36" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
@@ -3374,14 +3374,14 @@
       <c r="B89" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C89" s="36" t="s">
+      <c r="C89" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="D89" s="37"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="37"/>
-      <c r="G89" s="37"/>
-      <c r="H89" s="38"/>
+      <c r="D89" s="41"/>
+      <c r="E89" s="41"/>
+      <c r="F89" s="41"/>
+      <c r="G89" s="41"/>
+      <c r="H89" s="42"/>
     </row>
     <row r="90" spans="1:8" ht="90" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
@@ -3414,14 +3414,14 @@
       <c r="B91" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="C91" s="36" t="s">
+      <c r="C91" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="37"/>
-      <c r="G91" s="37"/>
-      <c r="H91" s="38"/>
+      <c r="D91" s="41"/>
+      <c r="E91" s="41"/>
+      <c r="F91" s="41"/>
+      <c r="G91" s="41"/>
+      <c r="H91" s="42"/>
     </row>
     <row r="92" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
@@ -3430,14 +3430,14 @@
       <c r="B92" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C92" s="36" t="s">
+      <c r="C92" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="D92" s="37"/>
-      <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="37"/>
-      <c r="H92" s="38"/>
+      <c r="D92" s="41"/>
+      <c r="E92" s="41"/>
+      <c r="F92" s="41"/>
+      <c r="G92" s="41"/>
+      <c r="H92" s="42"/>
     </row>
     <row r="93" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
@@ -3570,12 +3570,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" spans="1:4" s="23" customFormat="1" ht="36" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
@@ -3667,12 +3667,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="2" spans="1:4" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
@@ -3767,7 +3767,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -3779,16 +3779,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
     </row>
     <row r="2" spans="1:8" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
@@ -3840,7 +3840,7 @@
         <v>158</v>
       </c>
       <c r="H3" s="28">
-        <f t="shared" ref="H3:H19" si="0">E3*F3/1000</f>
+        <f t="shared" ref="H3:H21" si="0">E3*F3/1000</f>
         <v>0.77710000000000001</v>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
         <v>248</v>
       </c>
       <c r="E6" s="21">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6" s="21">
         <f>49.2+9.8</f>
@@ -3925,8 +3925,8 @@
         <v>158</v>
       </c>
       <c r="H6" s="28">
-        <f t="shared" ref="H6:H9" si="2">E6*F6/1000</f>
-        <v>0.47199999999999998</v>
+        <f t="shared" ref="H6:H8" si="2">E6*F6/1000</f>
+        <v>0.23599999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.3">
@@ -3940,21 +3940,21 @@
         <v>2</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E7" s="21">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F7" s="21">
-        <f>29.07+2.1+1.05</f>
-        <v>32.22</v>
+        <f>30.36+2.1+1.47</f>
+        <v>33.93</v>
       </c>
       <c r="G7" s="21" t="s">
         <v>158</v>
       </c>
       <c r="H7" s="28">
-        <f t="shared" si="2"/>
-        <v>3.2219999999999999E-2</v>
+        <f t="shared" ref="H7" si="3">E7*F7/1000</f>
+        <v>0.50895000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.3">
@@ -3968,21 +3968,21 @@
         <v>2</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E8" s="21">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F8" s="21">
-        <f>30.36+2.1+1.47</f>
-        <v>33.93</v>
+        <f>29.07+2.1+1.47</f>
+        <v>32.64</v>
       </c>
       <c r="G8" s="21" t="s">
         <v>158</v>
       </c>
       <c r="H8" s="28">
-        <f t="shared" ref="H8" si="3">E8*F8/1000</f>
-        <v>0.50895000000000001</v>
+        <f t="shared" si="2"/>
+        <v>6.5280000000000005E-2</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" x14ac:dyDescent="0.3">
@@ -3993,24 +3993,24 @@
         <v>1</v>
       </c>
       <c r="C9" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E9" s="21">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="21">
-        <f>29.07+2.1+1.47</f>
-        <v>32.64</v>
+        <f>35.8+2+3.1</f>
+        <v>40.9</v>
       </c>
       <c r="G9" s="21" t="s">
         <v>158</v>
       </c>
       <c r="H9" s="28">
-        <f t="shared" si="2"/>
-        <v>0.13056000000000001</v>
+        <f t="shared" ref="H9:H12" si="4">E9*F9/1000</f>
+        <v>0.32719999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18" x14ac:dyDescent="0.3">
@@ -4024,77 +4024,77 @@
         <v>3</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E10" s="21">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F10" s="21">
-        <f>35.8+2+3.1</f>
-        <v>40.9</v>
+        <f>49.2+9.8</f>
+        <v>59</v>
       </c>
       <c r="G10" s="21" t="s">
         <v>158</v>
       </c>
       <c r="H10" s="28">
-        <f t="shared" ref="H10" si="4">E10*F10/1000</f>
-        <v>0.32719999999999999</v>
+        <f t="shared" si="4"/>
+        <v>0.23599999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="25">
         <v>9</v>
       </c>
-      <c r="B11" s="30">
-        <v>2</v>
-      </c>
-      <c r="C11" s="30">
-        <v>1</v>
+      <c r="B11" s="29">
+        <v>1</v>
+      </c>
+      <c r="C11" s="29">
+        <v>3</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E11" s="21">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F11" s="21">
-        <f>35.4+1.7+3.1</f>
-        <v>40.200000000000003</v>
+        <f>29.07+2.1+1.05</f>
+        <v>32.22</v>
       </c>
       <c r="G11" s="21" t="s">
         <v>158</v>
       </c>
       <c r="H11" s="28">
-        <f>E11*F11/1000</f>
-        <v>0.3216</v>
+        <f t="shared" si="4"/>
+        <v>3.2219999999999999E-2</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="25">
         <v>10</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
+        <v>1</v>
+      </c>
+      <c r="C12" s="29">
+        <v>3</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="E12" s="21">
         <v>2</v>
       </c>
-      <c r="C12" s="30">
-        <v>1</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E12" s="21">
-        <v>12</v>
-      </c>
       <c r="F12" s="21">
-        <f>35.4+2.15+3.1</f>
-        <v>40.65</v>
+        <f>29.07+2.1+1.47</f>
+        <v>32.64</v>
       </c>
       <c r="G12" s="21" t="s">
         <v>158</v>
       </c>
       <c r="H12" s="28">
-        <f t="shared" si="0"/>
-        <v>0.48779999999999996</v>
+        <f t="shared" si="4"/>
+        <v>6.5280000000000005E-2</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="18" x14ac:dyDescent="0.3">
@@ -4105,13 +4105,13 @@
         <v>2</v>
       </c>
       <c r="C13" s="30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>239</v>
       </c>
       <c r="E13" s="21">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F13" s="21">
         <f>35.4+1.7+3.1</f>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="H13" s="28">
         <f>E13*F13/1000</f>
-        <v>0.64319999999999999</v>
+        <v>0.3216</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="18" x14ac:dyDescent="0.3">
@@ -4133,13 +4133,13 @@
         <v>2</v>
       </c>
       <c r="C14" s="30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>240</v>
       </c>
       <c r="E14" s="21">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F14" s="21">
         <f>35.4+2.15+3.1</f>
@@ -4149,25 +4149,25 @@
         <v>158</v>
       </c>
       <c r="H14" s="28">
-        <f t="shared" ref="H14:H18" si="5">E14*F14/1000</f>
-        <v>0.85365000000000002</v>
+        <f t="shared" si="0"/>
+        <v>0.48779999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="25">
         <v>13</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
+        <v>2</v>
+      </c>
+      <c r="C15" s="30">
         <v>3</v>
-      </c>
-      <c r="C15" s="31">
-        <v>1</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>239</v>
       </c>
       <c r="E15" s="21">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F15" s="21">
         <f>35.4+1.7+3.1</f>
@@ -4178,24 +4178,24 @@
       </c>
       <c r="H15" s="28">
         <f>E15*F15/1000</f>
-        <v>0.1608</v>
+        <v>0.64319999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="25">
         <v>14</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
+        <v>2</v>
+      </c>
+      <c r="C16" s="30">
         <v>3</v>
-      </c>
-      <c r="C16" s="31">
-        <v>1</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>240</v>
       </c>
       <c r="E16" s="21">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F16" s="21">
         <f>35.4+2.15+3.1</f>
@@ -4205,8 +4205,8 @@
         <v>158</v>
       </c>
       <c r="H16" s="28">
-        <f t="shared" si="5"/>
-        <v>0.24389999999999998</v>
+        <f t="shared" ref="H16:H20" si="5">E16*F16/1000</f>
+        <v>0.85365000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="18" x14ac:dyDescent="0.3">
@@ -4217,13 +4217,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>239</v>
       </c>
       <c r="E17" s="21">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F17" s="21">
         <f>35.4+1.7+3.1</f>
@@ -4233,8 +4233,8 @@
         <v>158</v>
       </c>
       <c r="H17" s="28">
-        <f t="shared" si="5"/>
-        <v>0.48240000000000005</v>
+        <f>E17*F17/1000</f>
+        <v>0.1608</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="18" x14ac:dyDescent="0.3">
@@ -4245,13 +4245,13 @@
         <v>3</v>
       </c>
       <c r="C18" s="31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>240</v>
       </c>
       <c r="E18" s="21">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F18" s="21">
         <f>35.4+2.15+3.1</f>
@@ -4262,24 +4262,24 @@
       </c>
       <c r="H18" s="28">
         <f t="shared" si="5"/>
-        <v>0.97559999999999991</v>
+        <v>0.24389999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="25">
         <v>17</v>
       </c>
-      <c r="B19" s="32">
-        <v>4</v>
-      </c>
-      <c r="C19" s="32">
+      <c r="B19" s="31">
+        <v>3</v>
+      </c>
+      <c r="C19" s="31">
         <v>3</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>239</v>
       </c>
       <c r="E19" s="21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F19" s="21">
         <f>35.4+1.7+3.1</f>
@@ -4289,25 +4289,25 @@
         <v>158</v>
       </c>
       <c r="H19" s="28">
-        <f t="shared" si="0"/>
-        <v>0.3216</v>
+        <f t="shared" si="5"/>
+        <v>0.48240000000000005</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
         <v>18</v>
       </c>
-      <c r="B20" s="32">
-        <v>4</v>
-      </c>
-      <c r="C20" s="32">
+      <c r="B20" s="31">
+        <v>3</v>
+      </c>
+      <c r="C20" s="31">
         <v>3</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>240</v>
       </c>
       <c r="E20" s="21">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F20" s="21">
         <f>35.4+2.15+3.1</f>
@@ -4317,24 +4317,80 @@
         <v>158</v>
       </c>
       <c r="H20" s="28">
-        <f t="shared" ref="H20" si="6">E20*F20/1000</f>
+        <f t="shared" si="5"/>
+        <v>0.97559999999999991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A21" s="25">
+        <v>19</v>
+      </c>
+      <c r="B21" s="32">
+        <v>4</v>
+      </c>
+      <c r="C21" s="32">
+        <v>3</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" s="21">
+        <v>8</v>
+      </c>
+      <c r="F21" s="21">
+        <f>35.4+1.7+3.1</f>
+        <v>40.200000000000003</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="H21" s="28">
+        <f t="shared" si="0"/>
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="25">
+        <v>20</v>
+      </c>
+      <c r="B22" s="32">
+        <v>4</v>
+      </c>
+      <c r="C22" s="32">
+        <v>3</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="E22" s="21">
+        <v>19</v>
+      </c>
+      <c r="F22" s="21">
+        <f>35.4+2.15+3.1</f>
+        <v>40.65</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="H22" s="28">
+        <f t="shared" ref="H22" si="6">E22*F22/1000</f>
         <v>0.77234999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A21" s="25"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21" t="s">
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="25"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="G21" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="H21" s="28">
-        <f>SUM(H3:H20)</f>
+      <c r="G23" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="H23" s="28">
+        <f>SUM(H3:H22)</f>
         <v>8.1442700000000006</v>
       </c>
     </row>
@@ -4360,16 +4416,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="47" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
     </row>
     <row r="2" spans="1:8" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
@@ -5396,10 +5452,10 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="46" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="46" customWidth="1"/>
-    <col min="3" max="4" width="8.88671875" style="45"/>
-    <col min="5" max="16384" width="8.88671875" style="46"/>
+    <col min="1" max="1" width="14.109375" style="38" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="38" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="37"/>
+    <col min="5" max="16384" width="8.88671875" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -5409,10 +5465,10 @@
       <c r="B1" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="36" t="s">
         <v>231</v>
       </c>
     </row>
@@ -5423,10 +5479,10 @@
       <c r="B2" s="34">
         <v>30</v>
       </c>
-      <c r="C2" s="44">
+      <c r="C2" s="36">
         <v>46.84</v>
       </c>
-      <c r="D2" s="44">
+      <c r="D2" s="36">
         <f>B2*C2</f>
         <v>1405.2</v>
       </c>
@@ -5438,10 +5494,10 @@
       <c r="B3" s="34">
         <v>16</v>
       </c>
-      <c r="C3" s="44">
+      <c r="C3" s="36">
         <v>22.4</v>
       </c>
-      <c r="D3" s="44">
+      <c r="D3" s="36">
         <f t="shared" ref="D3:D13" si="0">B3*C3</f>
         <v>358.4</v>
       </c>
@@ -5453,10 +5509,10 @@
       <c r="B4" s="34">
         <v>3</v>
       </c>
-      <c r="C4" s="44">
+      <c r="C4" s="36">
         <v>21.307692307692303</v>
       </c>
-      <c r="D4" s="44">
+      <c r="D4" s="36">
         <f t="shared" si="0"/>
         <v>63.923076923076906</v>
       </c>
@@ -5468,10 +5524,10 @@
       <c r="B5" s="34">
         <v>2</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="36">
         <v>56.629999999999995</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="36">
         <f t="shared" si="0"/>
         <v>113.25999999999999</v>
       </c>
@@ -5483,10 +5539,10 @@
       <c r="B6" s="34">
         <v>8</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="36">
         <v>18.690000000000001</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="36">
         <f t="shared" si="0"/>
         <v>149.52000000000001</v>
       </c>
@@ -5498,10 +5554,10 @@
       <c r="B7" s="34">
         <v>1</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="36">
         <v>18.690000000000001</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="36">
         <f t="shared" si="0"/>
         <v>18.690000000000001</v>
       </c>
@@ -5513,10 +5569,10 @@
       <c r="B8" s="34">
         <v>9</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="36">
         <v>12.170909090909092</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="36">
         <f t="shared" si="0"/>
         <v>109.53818181818183</v>
       </c>
@@ -5528,10 +5584,10 @@
       <c r="B9" s="34">
         <v>1</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="36">
         <v>5.44</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="36">
         <f t="shared" si="0"/>
         <v>5.44</v>
       </c>
@@ -5543,10 +5599,10 @@
       <c r="B10" s="34">
         <v>7</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="36">
         <v>6.93</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="36">
         <f t="shared" si="0"/>
         <v>48.51</v>
       </c>
@@ -5558,10 +5614,10 @@
       <c r="B11" s="34">
         <v>15</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="36">
         <v>8.81</v>
       </c>
-      <c r="D11" s="44">
+      <c r="D11" s="36">
         <f t="shared" si="0"/>
         <v>132.15</v>
       </c>
@@ -5573,10 +5629,10 @@
       <c r="B12" s="34">
         <v>1</v>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="36">
         <v>27.95</v>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="36">
         <f t="shared" si="0"/>
         <v>27.95</v>
       </c>
@@ -5588,24 +5644,24 @@
       <c r="B13" s="34">
         <v>3</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="36">
         <v>5.8500000000000005</v>
       </c>
-      <c r="D13" s="44">
+      <c r="D13" s="36">
         <f t="shared" si="0"/>
         <v>17.55</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="47"/>
-      <c r="B14" s="44">
+      <c r="A14" s="39"/>
+      <c r="B14" s="36">
         <f>SUM(B2:B13)</f>
         <v>96</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="36">
         <f>SUM(D2:D13)</f>
         <v>2450.131258741259</v>
       </c>
@@ -5644,7 +5700,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="19" customFormat="1" ht="54" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.35">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -5661,7 +5717,7 @@
         <v>26.36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="19" customFormat="1" ht="54" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.35">
       <c r="A3" s="25">
         <v>2</v>
       </c>

--- a/school_nagatinsky/walls/walls.xlsx
+++ b/school_nagatinsky/walls/walls.xlsx
@@ -22306,7 +22306,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -22591,6 +22591,13 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -22654,7 +22661,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -23250,12 +23257,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -23982,6 +24034,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -28004,7 +28077,7 @@
       <c r="H4" s="236"/>
       <c r="I4" s="49"/>
     </row>
-    <row r="5" spans="1:19" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54" t="s">
         <v>9</v>
       </c>
@@ -28077,8 +28150,8 @@
       <c r="E6" s="65"/>
       <c r="F6" s="65"/>
       <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="246"/>
       <c r="J6" s="95"/>
       <c r="K6" s="96"/>
       <c r="L6" s="96"/>
@@ -28108,10 +28181,10 @@
       <c r="G7" s="68">
         <v>1</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="73">
         <v>189.3</v>
       </c>
-      <c r="I7" s="73"/>
+      <c r="I7" s="247"/>
       <c r="J7" s="95"/>
       <c r="K7" s="96"/>
       <c r="L7" s="96"/>
@@ -28137,8 +28210,8 @@
       <c r="E8" s="65"/>
       <c r="F8" s="65"/>
       <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="73"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="247"/>
       <c r="J8" s="95"/>
       <c r="K8" s="96"/>
       <c r="L8" s="96"/>
@@ -28164,8 +28237,8 @@
       <c r="E9" s="65"/>
       <c r="F9" s="65"/>
       <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="73"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="247"/>
       <c r="J9" s="95"/>
       <c r="K9" s="96"/>
       <c r="L9" s="96"/>
@@ -28197,10 +28270,10 @@
       <c r="G10" s="68">
         <v>1</v>
       </c>
-      <c r="H10" s="68">
+      <c r="H10" s="73">
         <v>9.2200000000000006</v>
       </c>
-      <c r="I10" s="73">
+      <c r="I10" s="248">
         <f>SUM(Таблица1[[#This Row],[1.1-Ст]:[2.5-Ст]])</f>
         <v>11.013999999999999</v>
       </c>
@@ -28316,8 +28389,8 @@
       <c r="E15" s="65"/>
       <c r="F15" s="65"/>
       <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="73"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="249"/>
       <c r="J15" s="101"/>
       <c r="K15" s="102"/>
       <c r="L15" s="102"/>
@@ -28349,10 +28422,10 @@
       <c r="G16" s="68">
         <v>1</v>
       </c>
-      <c r="H16" s="68">
+      <c r="H16" s="73">
         <v>627.20000000000005</v>
       </c>
-      <c r="I16" s="73">
+      <c r="I16" s="248">
         <f>SUM(Таблица1[[#This Row],[1.1-Ст]:[2.5-Ст]])</f>
         <v>496.33124999999995</v>
       </c>
@@ -28489,8 +28562,8 @@
       <c r="E22" s="65"/>
       <c r="F22" s="65"/>
       <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="73"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="249"/>
       <c r="J22" s="101"/>
       <c r="K22" s="102"/>
       <c r="L22" s="102"/>
@@ -28516,8 +28589,8 @@
       <c r="E23" s="65"/>
       <c r="F23" s="65"/>
       <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="73"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="250"/>
       <c r="J23" s="95"/>
       <c r="K23" s="96"/>
       <c r="L23" s="96"/>
@@ -28543,8 +28616,8 @@
       <c r="E24" s="65"/>
       <c r="F24" s="65"/>
       <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="73"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="250"/>
       <c r="J24" s="95"/>
       <c r="K24" s="96"/>
       <c r="L24" s="96"/>
@@ -28576,10 +28649,10 @@
       <c r="G25" s="68">
         <v>1</v>
       </c>
-      <c r="H25" s="68">
+      <c r="H25" s="73">
         <v>261.11</v>
       </c>
-      <c r="I25" s="73">
+      <c r="I25" s="248">
         <f>SUM(Таблица1[[#This Row],[1.1-Ст]:[2.5-Ст]])</f>
         <v>204.49</v>
       </c>
@@ -28701,10 +28774,10 @@
       <c r="G30" s="68">
         <v>1</v>
       </c>
-      <c r="H30" s="68">
+      <c r="H30" s="73">
         <v>5</v>
       </c>
-      <c r="I30" s="73"/>
+      <c r="I30" s="251"/>
       <c r="J30" s="104"/>
       <c r="K30" s="105"/>
       <c r="L30" s="105"/>
@@ -28772,8 +28845,8 @@
       <c r="E33" s="65"/>
       <c r="F33" s="65"/>
       <c r="G33" s="65"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="73"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="249"/>
       <c r="J33" s="101"/>
       <c r="K33" s="102"/>
       <c r="L33" s="102"/>
@@ -28799,8 +28872,8 @@
       <c r="E34" s="65"/>
       <c r="F34" s="65"/>
       <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="73"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="250"/>
       <c r="J34" s="95"/>
       <c r="K34" s="96"/>
       <c r="L34" s="96"/>
@@ -28832,10 +28905,10 @@
       <c r="G35" s="68">
         <v>1</v>
       </c>
-      <c r="H35" s="68">
+      <c r="H35" s="73">
         <v>1964.75</v>
       </c>
-      <c r="I35" s="73">
+      <c r="I35" s="248">
         <f>SUM(Таблица1[[#This Row],[1.1-Ст]:[2.5-Ст]])</f>
         <v>855.51</v>
       </c>
@@ -28976,8 +29049,8 @@
       <c r="E41" s="65"/>
       <c r="F41" s="65"/>
       <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="72"/>
+      <c r="H41" s="72"/>
+      <c r="I41" s="246"/>
       <c r="J41" s="101"/>
       <c r="K41" s="102"/>
       <c r="L41" s="102"/>
@@ -29009,10 +29082,10 @@
       <c r="G42" s="68">
         <v>1</v>
       </c>
-      <c r="H42" s="68">
+      <c r="H42" s="73">
         <v>1519</v>
       </c>
-      <c r="I42" s="73"/>
+      <c r="I42" s="252"/>
       <c r="J42" s="98"/>
       <c r="K42" s="99"/>
       <c r="L42" s="99"/>
